--- a/plate3d/PLATE3D_BCJOINT_S.xlsx
+++ b/plate3d/PLATE3D_BCJOINT_S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="89">
   <si>
     <t># PLATE3D  ·  beam-to-column connection, written with SECT</t>
   </si>
@@ -91,18 +91,42 @@
     <t>L</t>
   </si>
   <si>
-    <t># BAR</t>
+    <t># BOLT</t>
   </si>
   <si>
     <t>dia</t>
   </si>
   <si>
-    <t>BAR</t>
+    <t>[hole]</t>
+  </si>
+  <si>
+    <t>[head_af]</t>
+  </si>
+  <si>
+    <t>[head_h]</t>
+  </si>
+  <si>
+    <t>[nut_af]</t>
+  </si>
+  <si>
+    <t>[nut_h]</t>
+  </si>
+  <si>
+    <t>#   the point on the MODULE row is the underside of the head, so these start</t>
+  </si>
+  <si>
+    <t>#   on the steel face and the head stands off behind it</t>
+  </si>
+  <si>
+    <t>BOLT</t>
   </si>
   <si>
     <t>bo.c</t>
   </si>
   <si>
+    <t>F10T</t>
+  </si>
+  <si>
     <t>bo.b</t>
   </si>
   <si>
@@ -158,6 +182,18 @@
   </si>
   <si>
     <t>#   drags the member back - which is what put the column at z 0..1600.</t>
+  </si>
+  <si>
+    <t>#   ROT.Z 90 turns the column so its FLANGES face the beam. Without it the</t>
+  </si>
+  <si>
+    <t>#   flanges face across and the beam lands on the web edge - which a 300x300</t>
+  </si>
+  <si>
+    <t>#   bounding box cannot show, being square either way. What showed it was</t>
+  </si>
+  <si>
+    <t>#   the bolts finding nothing to drill.</t>
   </si>
   <si>
     <t>MODULE</t>
@@ -629,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:P45"/>
+  <dimension ref="B1:P51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -823,7 +859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>26</v>
       </c>
@@ -839,500 +875,554 @@
       <c r="F12" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
+      <c r="G12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C13" t="s">
+      <c r="H12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13">
+      <c r="I12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15">
         <v>16</v>
       </c>
-      <c r="F13">
+      <c r="F15">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16">
+        <v>16</v>
+      </c>
+      <c r="F16">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14">
-        <v>16</v>
-      </c>
-      <c r="F14">
-        <v>47.5</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
-        <v>46</v>
+      <c r="M18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" t="s">
         <v>19</v>
       </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" t="s">
+        <v>63</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" t="s">
         <v>19</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F28" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" t="s">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" t="s">
         <v>23</v>
       </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" t="s">
-        <v>52</v>
-      </c>
-      <c r="E25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" t="s">
-        <v>57</v>
-      </c>
-      <c r="D30" t="s">
-        <v>29</v>
-      </c>
       <c r="F30">
-        <v>-57</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>54</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>40</v>
-      </c>
-      <c r="P30">
-        <v>2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D31" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F31" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B33" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" t="s">
-        <v>58</v>
-      </c>
-      <c r="D33" t="s">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36">
+        <v>-45</v>
+      </c>
+      <c r="G36">
+        <v>5</v>
+      </c>
+      <c r="H36">
         <v>30</v>
       </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="I33" t="s">
-        <v>59</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
+      <c r="I36" t="s">
+        <v>66</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
         <v>40</v>
       </c>
-      <c r="P33">
+      <c r="P36">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" t="s">
-        <v>52</v>
-      </c>
-      <c r="E34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F34" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="1" t="s">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="C37" t="s">
         <v>69</v>
       </c>
       <c r="D37" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E37" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B39" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" t="s">
         <v>70</v>
       </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>-800</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" t="s">
-        <v>69</v>
-      </c>
-      <c r="D38" t="s">
-        <v>53</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="D39" t="s">
+        <v>38</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39" t="s">
+        <v>71</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>40</v>
+      </c>
+      <c r="P39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" t="s">
         <v>70</v>
       </c>
-      <c r="F38">
-        <v>160</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B39" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B40" s="1" t="s">
+      <c r="D40" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="F40" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D41" t="s">
-        <v>57</v>
-      </c>
-      <c r="E41" t="s">
-        <v>70</v>
-      </c>
-      <c r="F41">
-        <v>180</v>
-      </c>
-      <c r="G41">
-        <v>33.25</v>
-      </c>
-      <c r="H41">
-        <v>-70</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="C42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D42" t="s">
-        <v>73</v>
-      </c>
-      <c r="E42" t="s">
+      <c r="E42" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42" t="s">
-        <v>59</v>
+      <c r="F42" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C43" t="s">
+        <v>81</v>
+      </c>
+      <c r="D43" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>-800</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44" t="s">
+        <v>81</v>
+      </c>
+      <c r="D44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E44" t="s">
+        <v>82</v>
+      </c>
+      <c r="F44">
+        <v>160</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B47" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C47" t="s">
+        <v>85</v>
+      </c>
+      <c r="D47" t="s">
         <v>69</v>
       </c>
-      <c r="D43" t="s">
-        <v>58</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="E47" t="s">
+        <v>82</v>
+      </c>
+      <c r="F47">
+        <v>180</v>
+      </c>
+      <c r="G47">
+        <v>33.25</v>
+      </c>
+      <c r="H47">
+        <v>-70</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B48" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C48" t="s">
+        <v>86</v>
+      </c>
+      <c r="D48" t="s">
+        <v>85</v>
+      </c>
+      <c r="E48" t="s">
+        <v>87</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B49" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C49" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" t="s">
         <v>70</v>
       </c>
-      <c r="F43">
+      <c r="E49" t="s">
+        <v>82</v>
+      </c>
+      <c r="F49">
         <v>185</v>
       </c>
-      <c r="G43">
-        <v>23.25</v>
-      </c>
-      <c r="H43">
+      <c r="G49">
+        <v>11.25</v>
+      </c>
+      <c r="H49">
         <v>-40</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B45" s="2" t="s">
-        <v>76</v>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/plate3d/PLATE3D_BCJOINT_S.xlsx
+++ b/plate3d/PLATE3D_BCJOINT_S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="93">
   <si>
     <t># PLATE3D  ·  beam-to-column connection, written with SECT</t>
   </si>
@@ -116,6 +116,18 @@
   </si>
   <si>
     <t>#   on the steel face and the head stands off behind it</t>
+  </si>
+  <si>
+    <t>#   length = grip + nut. The nut sits at the far end of the shank, so a bolt</t>
+  </si>
+  <si>
+    <t>#   written longer than that stands its nut off the steel - which is the right</t>
+  </si>
+  <si>
+    <t>#   way for a wrong length to show itself. Grip here is flange + cleat, and</t>
+  </si>
+  <si>
+    <t>#   cleat + web + cleat.</t>
   </si>
   <si>
     <t>BOLT</t>
@@ -665,7 +677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:P51"/>
+  <dimension ref="B1:P55"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -901,104 +913,104 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D15" t="s">
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E15">
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19">
         <v>16</v>
       </c>
-      <c r="F15">
+      <c r="F19">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20">
+        <v>16</v>
+      </c>
+      <c r="F20">
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B22" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16">
-        <v>16</v>
-      </c>
-      <c r="F16">
-        <v>42.5</v>
-      </c>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="N18" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O18" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P18" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
+      <c r="M22" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
+      <c r="N22" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
+      <c r="O22" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
+      <c r="P22" s="1" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1022,407 +1034,427 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C27" t="s">
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D27" t="s">
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" t="s">
         <v>19</v>
       </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27" t="s">
-        <v>63</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31" t="s">
+        <v>67</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" t="s">
-        <v>64</v>
-      </c>
-      <c r="E28" t="s">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" t="s">
+        <v>68</v>
+      </c>
+      <c r="E32" t="s">
         <v>19</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F32" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" t="s">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D30" t="s">
+      <c r="C34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" t="s">
         <v>23</v>
       </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="D31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E31" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="C35" t="s">
         <v>69</v>
       </c>
       <c r="D35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E35" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B39" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" t="s">
         <v>24</v>
       </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" t="s">
-        <v>69</v>
-      </c>
-      <c r="D36" t="s">
-        <v>36</v>
-      </c>
-      <c r="F36">
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40">
         <v>-45</v>
       </c>
-      <c r="G36">
+      <c r="G40">
         <v>5</v>
       </c>
-      <c r="H36">
+      <c r="H40">
         <v>30</v>
       </c>
-      <c r="I36" t="s">
-        <v>66</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
+      <c r="I40" t="s">
+        <v>70</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
         <v>40</v>
       </c>
-      <c r="P36">
+      <c r="P40">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" t="s">
-        <v>69</v>
-      </c>
-      <c r="D37" t="s">
-        <v>64</v>
-      </c>
-      <c r="E37" t="s">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" t="s">
+        <v>73</v>
+      </c>
+      <c r="D41" t="s">
+        <v>68</v>
+      </c>
+      <c r="E41" t="s">
         <v>24</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F41" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B39" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C39" t="s">
-        <v>70</v>
-      </c>
-      <c r="D39" t="s">
-        <v>38</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39" t="s">
-        <v>71</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43" t="s">
+        <v>75</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
         <v>40</v>
       </c>
-      <c r="P39">
+      <c r="P43">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" t="s">
-        <v>64</v>
-      </c>
-      <c r="E40" t="s">
-        <v>72</v>
-      </c>
-      <c r="F40" t="s">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" t="s">
+        <v>74</v>
+      </c>
+      <c r="D44" t="s">
+        <v>68</v>
+      </c>
+      <c r="E44" t="s">
+        <v>76</v>
+      </c>
+      <c r="F44" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" s="1" t="s">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B46" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H42" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="E46" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
+      <c r="F46" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C43" t="s">
+      <c r="G46" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D43" t="s">
-        <v>62</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="H46" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>-800</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" t="s">
-        <v>81</v>
-      </c>
-      <c r="D44" t="s">
-        <v>65</v>
-      </c>
-      <c r="E44" t="s">
-        <v>82</v>
-      </c>
-      <c r="F44">
-        <v>160</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B45" s="1" t="s">
+      <c r="I46" s="1" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B46" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C47" t="s">
         <v>85</v>
       </c>
       <c r="D47" t="s">
+        <v>66</v>
+      </c>
+      <c r="E47" t="s">
+        <v>86</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>-800</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B48" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C48" t="s">
+        <v>85</v>
+      </c>
+      <c r="D48" t="s">
         <v>69</v>
       </c>
-      <c r="E47" t="s">
-        <v>82</v>
-      </c>
-      <c r="F47">
+      <c r="E48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F48">
+        <v>160</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B51" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C51" t="s">
+        <v>89</v>
+      </c>
+      <c r="D51" t="s">
+        <v>73</v>
+      </c>
+      <c r="E51" t="s">
+        <v>86</v>
+      </c>
+      <c r="F51">
         <v>180</v>
       </c>
-      <c r="G47">
+      <c r="G51">
         <v>33.25</v>
       </c>
-      <c r="H47">
+      <c r="H51">
         <v>-70</v>
       </c>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B48" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C48" t="s">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B52" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C52" t="s">
+        <v>90</v>
+      </c>
+      <c r="D52" t="s">
+        <v>89</v>
+      </c>
+      <c r="E52" t="s">
+        <v>91</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C53" t="s">
+        <v>85</v>
+      </c>
+      <c r="D53" t="s">
+        <v>74</v>
+      </c>
+      <c r="E53" t="s">
         <v>86</v>
       </c>
-      <c r="D48" t="s">
-        <v>85</v>
-      </c>
-      <c r="E48" t="s">
-        <v>87</v>
-      </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B49" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C49" t="s">
-        <v>81</v>
-      </c>
-      <c r="D49" t="s">
-        <v>70</v>
-      </c>
-      <c r="E49" t="s">
-        <v>82</v>
-      </c>
-      <c r="F49">
+      <c r="F53">
         <v>185</v>
       </c>
-      <c r="G49">
+      <c r="G53">
         <v>11.25</v>
       </c>
-      <c r="H49">
+      <c r="H53">
         <v>-40</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" s="2" t="s">
-        <v>88</v>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/plate3d/PLATE3D_BCJOINT_S.xlsx
+++ b/plate3d/PLATE3D_BCJOINT_S.xlsx
@@ -118,7 +118,7 @@
     <t>#   on the steel face and the head stands off behind it</t>
   </si>
   <si>
-    <t>#   length = grip + nut. The nut sits at the far end of the shank, so a bolt</t>
+    <t>#   length = grip + nut + proj. proj is the thread showing past the nut, and</t>
   </si>
   <si>
     <t>#   written longer than that stands its nut off the steel - which is the right</t>
@@ -947,7 +947,7 @@
         <v>16</v>
       </c>
       <c r="F19">
-        <v>37.4</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
@@ -964,7 +964,7 @@
         <v>16</v>
       </c>
       <c r="F20">
-        <v>36.9</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.25">
